--- a/backend/data/financials_by_company/0098.HK.xlsx
+++ b/backend/data/financials_by_company/0098.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,580 +662,636 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-7486190.153042</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.142185</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1702431000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-52651000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-52651000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>826033000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>579868000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17090943000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1649780000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1069912000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-58488000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>104558000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>46070000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>871197809.846958</v>
-      </c>
-      <c r="P2" t="n">
-        <v>826033000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>17797199000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>1149721000</v>
+      </c>
       <c r="S2" t="n">
-        <v>420649134</v>
+        <v>420268000</v>
       </c>
       <c r="T2" t="n">
-        <v>420649134</v>
+        <v>418923000</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W2" t="n">
-        <v>826033000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>826033000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>826033000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-2062000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>828095000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>828095000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>137259000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>965354000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>13712000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-55293000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-12590000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>67883000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-58488000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>104558000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>46070000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1057442000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>706256000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-120152000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>847325000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>399438000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>447887000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1763698000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>17090943000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>18854641000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>18854641000</v>
-      </c>
+        <v>2.12</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-37288824.349056</v>
+        <v>-4248.47231</v>
       </c>
       <c r="C3" t="n">
-        <v>0.118105</v>
+        <v>0.098802</v>
       </c>
       <c r="D3" t="n">
-        <v>1840828000</v>
+        <v>1161684000</v>
       </c>
       <c r="E3" t="n">
-        <v>-315727000</v>
+        <v>-43000</v>
       </c>
       <c r="F3" t="n">
-        <v>-315727000</v>
+        <v>-43000</v>
       </c>
       <c r="G3" t="n">
-        <v>804171000</v>
+        <v>457774000</v>
       </c>
       <c r="H3" t="n">
-        <v>470722000</v>
+        <v>510883000</v>
       </c>
       <c r="I3" t="n">
-        <v>15362349000</v>
+        <v>15158361000</v>
       </c>
       <c r="J3" t="n">
-        <v>1525101000</v>
+        <v>1161641000</v>
       </c>
       <c r="K3" t="n">
-        <v>1054379000</v>
+        <v>650758000</v>
       </c>
       <c r="L3" t="n">
-        <v>-74836000</v>
+        <v>-79530000</v>
       </c>
       <c r="M3" t="n">
-        <v>138056000</v>
+        <v>138874000</v>
       </c>
       <c r="N3" t="n">
-        <v>63220000</v>
+        <v>59344000</v>
       </c>
       <c r="O3" t="n">
-        <v>1082609175.650944</v>
+        <v>457812751.52769</v>
       </c>
       <c r="P3" t="n">
-        <v>804171000</v>
+        <v>457774000</v>
       </c>
       <c r="Q3" t="n">
-        <v>16061044000</v>
+        <v>16369073000</v>
       </c>
       <c r="R3" t="n">
-        <v>1056298000</v>
+        <v>655774000</v>
       </c>
       <c r="S3" t="n">
-        <v>420649000</v>
+        <v>420110000</v>
       </c>
       <c r="T3" t="n">
-        <v>420649000</v>
+        <v>420110000</v>
       </c>
       <c r="U3" t="n">
-        <v>1.91</v>
+        <v>1.09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.91</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>804171000</v>
+        <v>457774000</v>
       </c>
       <c r="X3" t="n">
-        <v>804171000</v>
+        <v>457774000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>804171000</v>
+        <v>457774000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3930000</v>
+        <v>-3535000</v>
       </c>
       <c r="AB3" t="n">
-        <v>808101000</v>
+        <v>461309000</v>
       </c>
       <c r="AC3" t="n">
-        <v>808101000</v>
+        <v>461309000</v>
       </c>
       <c r="AD3" t="n">
-        <v>108222000</v>
+        <v>50575000</v>
       </c>
       <c r="AE3" t="n">
-        <v>916323000</v>
+        <v>511884000</v>
       </c>
       <c r="AF3" t="n">
-        <v>15815000</v>
+        <v>16696000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-308084000</v>
+        <v>6537000</v>
       </c>
       <c r="AH3" t="n">
-        <v>14880000</v>
+        <v>-6537000</v>
       </c>
       <c r="AI3" t="n">
-        <v>293204000</v>
+        <v>552098000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-74836000</v>
+        <v>-79530000</v>
       </c>
       <c r="AK3" t="n">
-        <v>138056000</v>
+        <v>138874000</v>
       </c>
       <c r="AL3" t="n">
-        <v>63220000</v>
+        <v>59344000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1291507000</v>
+        <v>563991000</v>
       </c>
       <c r="AN3" t="n">
-        <v>698695000</v>
+        <v>1210712000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-88750000</v>
+        <v>552098000</v>
       </c>
       <c r="AP3" t="n">
-        <v>813318000</v>
+        <v>698969000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>374054000</v>
+        <v>288446000</v>
       </c>
       <c r="AR3" t="n">
-        <v>439264000</v>
+        <v>410523000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1990202000</v>
+        <v>1774703000</v>
       </c>
       <c r="AT3" t="n">
-        <v>15362349000</v>
+        <v>15158361000</v>
       </c>
       <c r="AU3" t="n">
-        <v>17352551000</v>
+        <v>16933064000</v>
       </c>
       <c r="AV3" t="n">
-        <v>17352551000</v>
+        <v>16933064000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-54552459.297419</v>
+        <v>-2660070.854928</v>
       </c>
       <c r="C4" t="n">
-        <v>0.098802</v>
+        <v>0.118105</v>
       </c>
       <c r="D4" t="n">
-        <v>1713782000</v>
+        <v>1547624000</v>
       </c>
       <c r="E4" t="n">
-        <v>-552141000</v>
+        <v>-22523000</v>
       </c>
       <c r="F4" t="n">
-        <v>-552141000</v>
+        <v>-22523000</v>
       </c>
       <c r="G4" t="n">
-        <v>457774000</v>
+        <v>804171000</v>
       </c>
       <c r="H4" t="n">
-        <v>510883000</v>
+        <v>470722000</v>
       </c>
       <c r="I4" t="n">
-        <v>15158361000</v>
+        <v>15362349000</v>
       </c>
       <c r="J4" t="n">
-        <v>1161641000</v>
+        <v>1525101000</v>
       </c>
       <c r="K4" t="n">
-        <v>650758000</v>
+        <v>1054379000</v>
       </c>
       <c r="L4" t="n">
-        <v>-79530000</v>
+        <v>-74836000</v>
       </c>
       <c r="M4" t="n">
-        <v>138874000</v>
+        <v>138056000</v>
       </c>
       <c r="N4" t="n">
-        <v>59344000</v>
+        <v>63220000</v>
       </c>
       <c r="O4" t="n">
-        <v>955362540.702581</v>
+        <v>824033929.145072</v>
       </c>
       <c r="P4" t="n">
-        <v>457774000</v>
+        <v>804171000</v>
       </c>
       <c r="Q4" t="n">
-        <v>15816975000</v>
+        <v>16354248000</v>
       </c>
       <c r="R4" t="n">
-        <v>655774000</v>
+        <v>1056298000</v>
       </c>
       <c r="S4" t="n">
-        <v>420110000</v>
+        <v>420649000</v>
       </c>
       <c r="T4" t="n">
-        <v>420110000</v>
+        <v>420649000</v>
       </c>
       <c r="U4" t="n">
-        <v>1.09</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.91</v>
       </c>
       <c r="W4" t="n">
-        <v>457774000</v>
+        <v>804171000</v>
       </c>
       <c r="X4" t="n">
-        <v>457774000</v>
+        <v>804171000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>457774000</v>
+        <v>804171000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3535000</v>
+        <v>-3930000</v>
       </c>
       <c r="AB4" t="n">
-        <v>461309000</v>
+        <v>808101000</v>
       </c>
       <c r="AC4" t="n">
-        <v>461309000</v>
+        <v>808101000</v>
       </c>
       <c r="AD4" t="n">
-        <v>50575000</v>
+        <v>108222000</v>
       </c>
       <c r="AE4" t="n">
-        <v>511884000</v>
+        <v>916323000</v>
       </c>
       <c r="AF4" t="n">
-        <v>16696000</v>
+        <v>15815000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-545561000</v>
+        <v>-14880000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-6537000</v>
+        <v>14880000</v>
       </c>
       <c r="AI4" t="n">
-        <v>552098000</v>
+        <v>293204000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-79530000</v>
+        <v>-74836000</v>
       </c>
       <c r="AK4" t="n">
-        <v>138874000</v>
+        <v>138056000</v>
       </c>
       <c r="AL4" t="n">
-        <v>59344000</v>
+        <v>63220000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1116089000</v>
+        <v>998303000</v>
       </c>
       <c r="AN4" t="n">
-        <v>658614000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>991899000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>204454000</v>
+      </c>
       <c r="AP4" t="n">
-        <v>698969000</v>
+        <v>813318000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>288446000</v>
+        <v>374054000</v>
       </c>
       <c r="AR4" t="n">
-        <v>410523000</v>
+        <v>439264000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1774703000</v>
+        <v>1990202000</v>
       </c>
       <c r="AT4" t="n">
-        <v>15158361000</v>
+        <v>15362349000</v>
       </c>
       <c r="AU4" t="n">
-        <v>16933064000</v>
+        <v>17352551000</v>
       </c>
       <c r="AV4" t="n">
-        <v>16933064000</v>
+        <v>17352551000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-11424508.282308</v>
+        <v>2165764.152839</v>
       </c>
       <c r="C5" t="n">
-        <v>0.159291</v>
+        <v>0.142185</v>
       </c>
       <c r="D5" t="n">
-        <v>1612064000</v>
+        <v>1634548000</v>
       </c>
       <c r="E5" t="n">
-        <v>-71721000</v>
+        <v>15232000</v>
       </c>
       <c r="F5" t="n">
-        <v>-71721000</v>
+        <v>15232000</v>
       </c>
       <c r="G5" t="n">
-        <v>887800000</v>
+        <v>826033000</v>
       </c>
       <c r="H5" t="n">
-        <v>384079000</v>
+        <v>579868000</v>
       </c>
       <c r="I5" t="n">
-        <v>13621056000</v>
+        <v>17090943000</v>
       </c>
       <c r="J5" t="n">
-        <v>1540343000</v>
+        <v>1649780000</v>
       </c>
       <c r="K5" t="n">
-        <v>1156264000</v>
+        <v>1069912000</v>
       </c>
       <c r="L5" t="n">
-        <v>-22980000</v>
+        <v>-58488000</v>
       </c>
       <c r="M5" t="n">
-        <v>101063000</v>
+        <v>104558000</v>
       </c>
       <c r="N5" t="n">
-        <v>78083000</v>
+        <v>46070000</v>
       </c>
       <c r="O5" t="n">
-        <v>948096491.717692</v>
+        <v>812966764.1528389</v>
       </c>
       <c r="P5" t="n">
-        <v>887800000</v>
+        <v>826033000</v>
       </c>
       <c r="Q5" t="n">
-        <v>14289102000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1149721000</v>
-      </c>
+        <v>17865082000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>420268000</v>
+        <v>420649000</v>
       </c>
       <c r="T5" t="n">
-        <v>418923000</v>
+        <v>420649000</v>
       </c>
       <c r="U5" t="n">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="W5" t="n">
-        <v>887800000</v>
+        <v>826033000</v>
       </c>
       <c r="X5" t="n">
-        <v>887800000</v>
+        <v>826033000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>887800000</v>
+        <v>826033000</v>
       </c>
       <c r="AA5" t="n">
-        <v>683000</v>
+        <v>-2062000</v>
       </c>
       <c r="AB5" t="n">
-        <v>887117000</v>
+        <v>828095000</v>
       </c>
       <c r="AC5" t="n">
-        <v>887117000</v>
+        <v>828095000</v>
       </c>
       <c r="AD5" t="n">
-        <v>168084000</v>
+        <v>137259000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1055201000</v>
+        <v>965354000</v>
       </c>
       <c r="AF5" t="n">
-        <v>14764000</v>
+        <v>13712000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-76310000</v>
+        <v>12590000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-3145000</v>
+        <v>-12590000</v>
       </c>
       <c r="AI5" t="n">
-        <v>79455000</v>
+        <v>67883000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-22980000</v>
+        <v>-58488000</v>
       </c>
       <c r="AK5" t="n">
-        <v>101063000</v>
+        <v>104558000</v>
       </c>
       <c r="AL5" t="n">
-        <v>78083000</v>
+        <v>46070000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1143798000</v>
+        <v>989559000</v>
       </c>
       <c r="AN5" t="n">
-        <v>668046000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>774139000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-52269000</v>
+      </c>
       <c r="AP5" t="n">
-        <v>715651000</v>
+        <v>847325000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>314575000</v>
+        <v>399438000</v>
       </c>
       <c r="AR5" t="n">
-        <v>401076000</v>
+        <v>447887000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1811844000</v>
+        <v>1763698000</v>
       </c>
       <c r="AT5" t="n">
-        <v>13621056000</v>
+        <v>17090943000</v>
       </c>
       <c r="AU5" t="n">
-        <v>15432900000</v>
+        <v>18854641000</v>
       </c>
       <c r="AV5" t="n">
-        <v>15432900000</v>
+        <v>18854641000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-343667.534273</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.151931</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1507099000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2262000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2262000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>632219000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>658976000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>19399383000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1504837000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>845861000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-15219000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>103589000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>88370000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>634137332.465727</v>
+      </c>
+      <c r="P6" t="n">
+        <v>632219000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>19949373000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>632219000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>632219000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>632219000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2721000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>629498000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>629498000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>112774000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>742272000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10983000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>206000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-206000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-57220000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-15219000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>103589000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>88370000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>751162000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>549990000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-166989000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>737388000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>316333000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>421055000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1301152000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>19399383000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>20700535000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>20700535000</v>
       </c>
     </row>
   </sheetData>
@@ -1249,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,211 +1649,93 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>420649134</v>
-      </c>
-      <c r="C2" t="n">
-        <v>420649134</v>
-      </c>
-      <c r="D2" t="n">
-        <v>151291000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2879677000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5449336000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8775226000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3767978000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5449336000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2326000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5897875000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>8148207000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5907460000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>9585000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5897875000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>5100929000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>148239000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3753000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3753000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>8634980000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2388908000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>117570000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>20675000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2250663000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>331000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2250332000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>6246072000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>629014000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1995000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>627019000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>35206000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4953050000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>453717000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>37716000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4461617000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>14542440000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>4528390000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>72700000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>214098000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6957000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>23462000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23462000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>197920000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>448539000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>448539000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3564714000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-3961925000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7526639000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>281735000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12210000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5368347000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1864347000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>10014050000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>196062000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>155702000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1654256000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1109320000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>307600000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>237336000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>342510000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4939460000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>2726060000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>2726060000</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
+        <v>15289000</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="n">
+        <v>1643133000</v>
+      </c>
+      <c r="BR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>420649134</v>
@@ -1806,43 +1744,43 @@
         <v>420649134</v>
       </c>
       <c r="D3" t="n">
-        <v>307077000</v>
+        <v>649233000</v>
       </c>
       <c r="E3" t="n">
-        <v>3153547000</v>
+        <v>2507057000</v>
       </c>
       <c r="F3" t="n">
-        <v>4855351000</v>
+        <v>4253757000</v>
       </c>
       <c r="G3" t="n">
-        <v>8465800000</v>
+        <v>7150877000</v>
       </c>
       <c r="H3" t="n">
-        <v>3832080000</v>
+        <v>3032150000</v>
       </c>
       <c r="I3" t="n">
-        <v>4855351000</v>
+        <v>4253757000</v>
       </c>
       <c r="J3" t="n">
-        <v>6055000</v>
+        <v>8051000</v>
       </c>
       <c r="K3" t="n">
-        <v>5318308000</v>
+        <v>4651871000</v>
       </c>
       <c r="L3" t="n">
-        <v>7966210000</v>
+        <v>6600425000</v>
       </c>
       <c r="M3" t="n">
-        <v>5325831000</v>
+        <v>4655464000</v>
       </c>
       <c r="N3" t="n">
-        <v>7523000</v>
+        <v>3593000</v>
       </c>
       <c r="O3" t="n">
-        <v>5318308000</v>
+        <v>4651871000</v>
       </c>
       <c r="P3" t="n">
-        <v>4528504000</v>
+        <v>3872876000</v>
       </c>
       <c r="Q3" t="n">
         <v>148239000</v>
@@ -1854,159 +1792,160 @@
         <v>3753000</v>
       </c>
       <c r="T3" t="n">
-        <v>7540395000</v>
+        <v>7440507000</v>
       </c>
       <c r="U3" t="n">
-        <v>2745460000</v>
+        <v>2017457000</v>
       </c>
       <c r="V3" t="n">
-        <v>66118000</v>
+        <v>41579000</v>
       </c>
       <c r="W3" t="n">
-        <v>27903000</v>
+        <v>21700000</v>
       </c>
       <c r="X3" t="n">
-        <v>2651439000</v>
+        <v>1954178000</v>
       </c>
       <c r="Y3" t="n">
-        <v>3537000</v>
+        <v>5624000</v>
       </c>
       <c r="Z3" t="n">
-        <v>2647902000</v>
+        <v>1948554000</v>
       </c>
       <c r="AA3" t="n">
-        <v>4794935000</v>
+        <v>5423050000</v>
       </c>
       <c r="AB3" t="n">
-        <v>502108000</v>
+        <v>552879000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2518000</v>
+        <v>2427000</v>
       </c>
       <c r="AD3" t="n">
-        <v>499590000</v>
+        <v>550452000</v>
       </c>
       <c r="AE3" t="n">
-        <v>38055000</v>
+        <v>45747000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3606389000</v>
+        <v>4190098000</v>
       </c>
       <c r="AG3" t="n">
-        <v>511436000</v>
+        <v>495553000</v>
       </c>
       <c r="AH3" t="n">
-        <v>88201000</v>
+        <v>70885000</v>
       </c>
       <c r="AI3" t="n">
-        <v>3006752000</v>
+        <v>3623660000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12866226000</v>
+        <v>12095971000</v>
       </c>
       <c r="AK3" t="n">
-        <v>4239211000</v>
+        <v>3640771000</v>
       </c>
       <c r="AL3" t="n">
-        <v>31432000</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>201919000</v>
+        <v>145621000</v>
       </c>
       <c r="AN3" t="n">
-        <v>4315000</v>
+        <v>8556000</v>
       </c>
       <c r="AO3" t="n">
-        <v>36508000</v>
+        <v>32847000</v>
       </c>
       <c r="AP3" t="n">
-        <v>36508000</v>
+        <v>32847000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>3959000</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>3959000</v>
       </c>
       <c r="AS3" t="n">
-        <v>193580000</v>
+        <v>199052000</v>
       </c>
       <c r="AT3" t="n">
-        <v>462957000</v>
+        <v>398114000</v>
       </c>
       <c r="AU3" t="n">
-        <v>462957000</v>
+        <v>398114000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3308500000</v>
+        <v>2852622000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-3410762000</v>
+        <v>-3013184000</v>
       </c>
       <c r="AX3" t="n">
-        <v>6719262000</v>
+        <v>5865806000</v>
       </c>
       <c r="AY3" t="n">
-        <v>465134000</v>
+        <v>235510000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12210000</v>
+        <v>11913000</v>
       </c>
       <c r="BA3" t="n">
-        <v>4635563000</v>
+        <v>4181171000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1606355000</v>
+        <v>1437212000</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>8627015000</v>
+        <v>8455200000</v>
       </c>
       <c r="BE3" t="n">
+        <v>3402000</v>
+      </c>
+      <c r="BF3" t="n">
         <v>0</v>
       </c>
-      <c r="BF3" t="n">
-        <v>2040000</v>
-      </c>
       <c r="BG3" t="n">
-        <v>124250000</v>
+        <v>224736000</v>
       </c>
       <c r="BH3" t="n">
-        <v>107102000</v>
+        <v>172381000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1362123000</v>
+        <v>1453525000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>975948000</v>
+        <v>1049729000</v>
       </c>
       <c r="BK3" t="n">
-        <v>170684000</v>
+        <v>150152000</v>
       </c>
       <c r="BL3" t="n">
-        <v>215491000</v>
+        <v>253644000</v>
       </c>
       <c r="BM3" t="n">
-        <v>195476000</v>
+        <v>159451000</v>
       </c>
       <c r="BN3" t="n">
-        <v>3995609000</v>
+        <v>4591932000</v>
       </c>
       <c r="BO3" t="n">
-        <v>2840415000</v>
+        <v>1849773000</v>
       </c>
       <c r="BP3" t="n">
-        <v>2840415000</v>
+        <v>1849773000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2840415000</v>
-      </c>
+        <v>1849773000</v>
+      </c>
+      <c r="BR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>420649134</v>
@@ -2015,43 +1954,43 @@
         <v>420649134</v>
       </c>
       <c r="D4" t="n">
-        <v>649233000</v>
+        <v>307077000</v>
       </c>
       <c r="E4" t="n">
-        <v>2507057000</v>
+        <v>3153547000</v>
       </c>
       <c r="F4" t="n">
-        <v>4253757000</v>
+        <v>4855351000</v>
       </c>
       <c r="G4" t="n">
-        <v>7150877000</v>
+        <v>8465800000</v>
       </c>
       <c r="H4" t="n">
-        <v>3032150000</v>
+        <v>3832080000</v>
       </c>
       <c r="I4" t="n">
-        <v>4253757000</v>
+        <v>4855351000</v>
       </c>
       <c r="J4" t="n">
-        <v>8051000</v>
+        <v>6055000</v>
       </c>
       <c r="K4" t="n">
-        <v>4651871000</v>
+        <v>5318308000</v>
       </c>
       <c r="L4" t="n">
-        <v>6600425000</v>
+        <v>7966210000</v>
       </c>
       <c r="M4" t="n">
-        <v>4655464000</v>
+        <v>5325831000</v>
       </c>
       <c r="N4" t="n">
-        <v>3593000</v>
+        <v>7523000</v>
       </c>
       <c r="O4" t="n">
-        <v>4651871000</v>
+        <v>5318308000</v>
       </c>
       <c r="P4" t="n">
-        <v>3872876000</v>
+        <v>4528504000</v>
       </c>
       <c r="Q4" t="n">
         <v>148239000</v>
@@ -2063,359 +2002,567 @@
         <v>3753000</v>
       </c>
       <c r="T4" t="n">
-        <v>7440507000</v>
+        <v>7540395000</v>
       </c>
       <c r="U4" t="n">
-        <v>2017457000</v>
+        <v>2745460000</v>
       </c>
       <c r="V4" t="n">
-        <v>41579000</v>
+        <v>66118000</v>
       </c>
       <c r="W4" t="n">
-        <v>21700000</v>
+        <v>27903000</v>
       </c>
       <c r="X4" t="n">
-        <v>1954178000</v>
+        <v>2651439000</v>
       </c>
       <c r="Y4" t="n">
-        <v>5624000</v>
+        <v>3537000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1948554000</v>
+        <v>2647902000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5423050000</v>
+        <v>4794935000</v>
       </c>
       <c r="AB4" t="n">
-        <v>552879000</v>
+        <v>502108000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2427000</v>
+        <v>2518000</v>
       </c>
       <c r="AD4" t="n">
-        <v>550452000</v>
+        <v>499590000</v>
       </c>
       <c r="AE4" t="n">
-        <v>45747000</v>
+        <v>38055000</v>
       </c>
       <c r="AF4" t="n">
-        <v>4190098000</v>
+        <v>3606389000</v>
       </c>
       <c r="AG4" t="n">
-        <v>495553000</v>
+        <v>511436000</v>
       </c>
       <c r="AH4" t="n">
-        <v>70885000</v>
+        <v>88201000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3623660000</v>
+        <v>3006752000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12095971000</v>
+        <v>12866226000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3640771000</v>
+        <v>4239211000</v>
       </c>
       <c r="AL4" t="n">
+        <v>31432000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>201919000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4315000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>36508000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>36508000</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>0</v>
       </c>
-      <c r="AM4" t="n">
-        <v>145621000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>8556000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>32847000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>32847000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3959000</v>
-      </c>
       <c r="AR4" t="n">
-        <v>3959000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>199052000</v>
+        <v>193580000</v>
       </c>
       <c r="AT4" t="n">
-        <v>398114000</v>
+        <v>462957000</v>
       </c>
       <c r="AU4" t="n">
-        <v>398114000</v>
+        <v>462957000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2852622000</v>
+        <v>3308500000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-3013184000</v>
+        <v>-3410762000</v>
       </c>
       <c r="AX4" t="n">
-        <v>5865806000</v>
+        <v>6719262000</v>
       </c>
       <c r="AY4" t="n">
-        <v>235510000</v>
+        <v>465134000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11913000</v>
+        <v>12210000</v>
       </c>
       <c r="BA4" t="n">
-        <v>4181171000</v>
+        <v>4635563000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1437212000</v>
+        <v>1606355000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>8455200000</v>
+        <v>8627015000</v>
       </c>
       <c r="BE4" t="n">
-        <v>3402000</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>2040000</v>
       </c>
       <c r="BG4" t="n">
-        <v>224736000</v>
+        <v>124250000</v>
       </c>
       <c r="BH4" t="n">
-        <v>172381000</v>
+        <v>107102000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1453525000</v>
+        <v>1362123000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1049729000</v>
+        <v>975948000</v>
       </c>
       <c r="BK4" t="n">
-        <v>150152000</v>
+        <v>170684000</v>
       </c>
       <c r="BL4" t="n">
-        <v>253644000</v>
+        <v>215491000</v>
       </c>
       <c r="BM4" t="n">
-        <v>159451000</v>
+        <v>195476000</v>
       </c>
       <c r="BN4" t="n">
-        <v>4591932000</v>
+        <v>3995609000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1849773000</v>
+        <v>2840415000</v>
       </c>
       <c r="BP4" t="n">
-        <v>1849773000</v>
+        <v>2840415000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1849773000</v>
-      </c>
+        <v>2840415000</v>
+      </c>
+      <c r="BR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>419496334</v>
+        <v>420649134</v>
       </c>
       <c r="C5" t="n">
-        <v>419496334</v>
+        <v>420649134</v>
       </c>
       <c r="D5" t="n">
-        <v>108226000</v>
+        <v>151291000</v>
       </c>
       <c r="E5" t="n">
-        <v>1758811000</v>
+        <v>2879677000</v>
       </c>
       <c r="F5" t="n">
-        <v>4151780000</v>
+        <v>5449336000</v>
       </c>
       <c r="G5" t="n">
-        <v>6230701000</v>
+        <v>8775226000</v>
       </c>
       <c r="H5" t="n">
-        <v>2673049000</v>
+        <v>3767978000</v>
       </c>
       <c r="I5" t="n">
-        <v>4151780000</v>
+        <v>5449336000</v>
       </c>
       <c r="J5" t="n">
-        <v>7452000</v>
+        <v>2326000</v>
       </c>
       <c r="K5" t="n">
-        <v>4479342000</v>
+        <v>5897875000</v>
       </c>
       <c r="L5" t="n">
-        <v>5738084000</v>
+        <v>8148207000</v>
       </c>
       <c r="M5" t="n">
-        <v>4479400000</v>
+        <v>5907460000</v>
       </c>
       <c r="N5" t="n">
-        <v>58000</v>
+        <v>9585000</v>
       </c>
       <c r="O5" t="n">
-        <v>4479342000</v>
+        <v>5897875000</v>
       </c>
       <c r="P5" t="n">
-        <v>3662303000</v>
+        <v>5100929000</v>
       </c>
       <c r="Q5" t="n">
-        <v>188048000</v>
+        <v>148239000</v>
       </c>
       <c r="R5" t="n">
-        <v>3744000</v>
+        <v>3753000</v>
       </c>
       <c r="S5" t="n">
-        <v>3744000</v>
+        <v>3753000</v>
       </c>
       <c r="T5" t="n">
-        <v>6862788000</v>
+        <v>8634980000</v>
       </c>
       <c r="U5" t="n">
-        <v>1319703000</v>
+        <v>2388908000</v>
       </c>
       <c r="V5" t="n">
-        <v>25566000</v>
+        <v>117570000</v>
       </c>
       <c r="W5" t="n">
-        <v>29948000</v>
+        <v>20675000</v>
       </c>
       <c r="X5" t="n">
-        <v>1264189000</v>
+        <v>2250663000</v>
       </c>
       <c r="Y5" t="n">
-        <v>5447000</v>
+        <v>331000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1258742000</v>
+        <v>2250332000</v>
       </c>
       <c r="AA5" t="n">
-        <v>5543085000</v>
+        <v>6246072000</v>
       </c>
       <c r="AB5" t="n">
-        <v>494622000</v>
+        <v>629014000</v>
       </c>
       <c r="AC5" t="n">
-        <v>2005000</v>
+        <v>1995000</v>
       </c>
       <c r="AD5" t="n">
-        <v>492617000</v>
+        <v>627019000</v>
       </c>
       <c r="AE5" t="n">
-        <v>33381000</v>
+        <v>35206000</v>
       </c>
       <c r="AF5" t="n">
-        <v>4505493000</v>
+        <v>4953050000</v>
       </c>
       <c r="AG5" t="n">
-        <v>423668000</v>
+        <v>453717000</v>
       </c>
       <c r="AH5" t="n">
-        <v>89057000</v>
+        <v>37716000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3992768000</v>
+        <v>4461617000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11342188000</v>
+        <v>14542440000</v>
       </c>
       <c r="AK5" t="n">
-        <v>3126054000</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>4528390000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>72700000</v>
+      </c>
       <c r="AM5" t="n">
-        <v>68434000</v>
+        <v>214098000</v>
       </c>
       <c r="AN5" t="n">
+        <v>6957000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>23462000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>23462000</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>0</v>
       </c>
-      <c r="AO5" t="n">
-        <v>11183000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11183000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>8975000</v>
-      </c>
       <c r="AR5" t="n">
-        <v>8975000</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>169427000</v>
+        <v>197920000</v>
       </c>
       <c r="AT5" t="n">
-        <v>327562000</v>
+        <v>448539000</v>
       </c>
       <c r="AU5" t="n">
-        <v>327562000</v>
+        <v>448539000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2540473000</v>
+        <v>3564714000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-2559859000</v>
+        <v>-3961925000</v>
       </c>
       <c r="AX5" t="n">
-        <v>5100332000</v>
+        <v>7526639000</v>
       </c>
       <c r="AY5" t="n">
-        <v>224130000</v>
+        <v>281735000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11665000</v>
+        <v>12210000</v>
       </c>
       <c r="BA5" t="n">
-        <v>3474828000</v>
+        <v>5368347000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1389709000</v>
+        <v>1864347000</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>8216134000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>15289000</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+        <v>10014050000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
       <c r="BG5" t="n">
-        <v>208919000</v>
+        <v>196062000</v>
       </c>
       <c r="BH5" t="n">
-        <v>199421000</v>
+        <v>155702000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1481803000</v>
+        <v>1654256000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>861491000</v>
+        <v>1109320000</v>
       </c>
       <c r="BK5" t="n">
-        <v>146574000</v>
+        <v>307600000</v>
       </c>
       <c r="BL5" t="n">
-        <v>473738000</v>
+        <v>237336000</v>
       </c>
       <c r="BM5" t="n">
-        <v>141414000</v>
+        <v>342510000</v>
       </c>
       <c r="BN5" t="n">
-        <v>4526155000</v>
+        <v>4939460000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1643133000</v>
+        <v>2726060000</v>
       </c>
       <c r="BP5" t="n">
-        <v>1643133000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1643133000</v>
+        <v>2726060000</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>420649134</v>
+      </c>
+      <c r="C6" t="n">
+        <v>420649134</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1317314000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3016206000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5841005000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9249550000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3752480000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5841005000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>51014000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6284358000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8770235000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6287180000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2822000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6284358000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5483162000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>148239000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3753000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3753000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8706777000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2683675000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>131161000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12825000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2532480000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>46603000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2485877000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6023102000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>483726000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4411000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>479315000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>32534000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4770650000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>696401000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>32760000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4041489000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14993957000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5218375000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>53191000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>214034000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4489000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>551045000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>551045000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7905000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7905000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>179024000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>443353000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>443353000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3765334000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-4582352000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8347686000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>87253000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>77291000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6223020000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1960122000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9775582000</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
+        <v>326115000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>137016000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1986447000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1148664000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>232674000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>605109000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>310450000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4806320000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2209234000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1647878000</v>
+      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="n">
+        <v>561356000</v>
       </c>
     </row>
   </sheetData>
@@ -2429,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2683,229 +2830,161 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Net Other Financing Charges</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>459664000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-2263734000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1993593000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>-955826000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2726060000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2840415000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2681000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-117036000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-647877000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-128378000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-245629000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-245629000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>-270141000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-270141000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-2263734000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1993593000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-884649000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-21881000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>46070000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>11186000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11186000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-951024000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4802000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-955826000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1415490000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-206871000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-29453000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-33411000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1522459000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-48600000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-295133000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-1174768000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>52879000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>579868000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1062000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>578806000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-2642000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-1938000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>370000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-12960000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>965354000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>6084000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>6084000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6084000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>27655000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>-854000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>627000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>485690000</v>
+        <v>-184330000</v>
       </c>
       <c r="C3" t="n">
-        <v>-2122750000</v>
+        <v>-2780017000</v>
       </c>
       <c r="D3" t="n">
-        <v>2771236000</v>
+        <v>3527664000</v>
       </c>
       <c r="E3" t="n">
+        <v>5838000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-975097000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1849773000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1643133000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-20252000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>226892000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>326514000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-139567000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-285419000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-285419000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5838000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5838000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>747647000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>747647000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-2780017000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3527664000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-890389000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>146052000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>59344000</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>-980917000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2840415000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1849773000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2046000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>988596000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>358690000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-146456000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-141047000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-141047000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>648486000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>648486000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-2122750000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2771236000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-836701000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>100486000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>63220000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-24316000</v>
+        <v>-141000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>5200000</v>
+        <v>161869000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-29516000</v>
+        <v>-141000000</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -2913,152 +2992,153 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="n">
-        <v>-976091000</v>
+        <v>-954785000</v>
       </c>
       <c r="AF3" t="n">
-        <v>4826000</v>
+        <v>20312000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-980917000</v>
+        <v>-975097000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1466607000</v>
+        <v>790767000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-141550000</v>
+        <v>-153223000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-220962000</v>
+        <v>-726171000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3896000</v>
+        <v>161717000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-584102000</v>
+        <v>-306733000</v>
       </c>
       <c r="AM3" t="n">
-        <v>56455000</v>
+        <v>88144000</v>
       </c>
       <c r="AN3" t="n">
-        <v>68777000</v>
+        <v>163835000</v>
       </c>
       <c r="AO3" t="n">
-        <v>234012000</v>
+        <v>-833134000</v>
       </c>
       <c r="AP3" t="n">
-        <v>64941000</v>
+        <v>79530000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-1690000</v>
       </c>
       <c r="AR3" t="n">
-        <v>470722000</v>
+        <v>510883000</v>
       </c>
       <c r="AS3" t="n">
         <v>412000</v>
       </c>
       <c r="AT3" t="n">
-        <v>470310000</v>
+        <v>510471000</v>
       </c>
       <c r="AU3" t="n">
-        <v>7643000</v>
+        <v>3178000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1844000</v>
+        <v>15799000</v>
       </c>
       <c r="AW3" t="n">
-        <v>14880000</v>
+        <v>-6537000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>916323000</v>
-      </c>
+        <v>511884000</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-184330000</v>
+        <v>485690000</v>
       </c>
       <c r="C4" t="n">
-        <v>-2780017000</v>
+        <v>-2122750000</v>
       </c>
       <c r="D4" t="n">
-        <v>3527664000</v>
+        <v>2771236000</v>
       </c>
       <c r="E4" t="n">
-        <v>5838000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-975097000</v>
+        <v>-980917000</v>
       </c>
       <c r="G4" t="n">
+        <v>2840415000</v>
+      </c>
+      <c r="H4" t="n">
         <v>1849773000</v>
       </c>
-      <c r="H4" t="n">
-        <v>1643133000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-20252000</v>
+        <v>2046000</v>
       </c>
       <c r="J4" t="n">
-        <v>226892000</v>
+        <v>988596000</v>
       </c>
       <c r="K4" t="n">
-        <v>326514000</v>
+        <v>358690000</v>
       </c>
       <c r="L4" t="n">
-        <v>-139567000</v>
+        <v>-146456000</v>
       </c>
       <c r="M4" t="n">
-        <v>-285419000</v>
+        <v>-141047000</v>
       </c>
       <c r="N4" t="n">
-        <v>-285419000</v>
+        <v>-141047000</v>
       </c>
       <c r="O4" t="n">
-        <v>5838000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5838000</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>747647000</v>
+        <v>648486000</v>
       </c>
       <c r="R4" t="n">
-        <v>747647000</v>
+        <v>648486000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2780017000</v>
+        <v>-2122750000</v>
       </c>
       <c r="T4" t="n">
-        <v>3527664000</v>
+        <v>2771236000</v>
       </c>
       <c r="U4" t="n">
-        <v>-890389000</v>
+        <v>-836701000</v>
       </c>
       <c r="V4" t="n">
-        <v>146052000</v>
+        <v>100486000</v>
       </c>
       <c r="W4" t="n">
-        <v>59344000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
+        <v>63220000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-141000000</v>
+        <v>-24316000</v>
       </c>
       <c r="Z4" t="n">
-        <v>161869000</v>
+        <v>5200000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-141000000</v>
+        <v>-29516000</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3066,226 +3146,364 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>-976091000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>4826000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-980917000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1466607000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-141550000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-220962000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3896000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-584102000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>56455000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>68777000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>234012000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>64941000</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="n">
-        <v>-954785000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>20312000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-975097000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>790767000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-153223000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-726171000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>161717000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-306733000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>88144000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>163835000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-833134000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>79530000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-1690000</v>
-      </c>
       <c r="AR4" t="n">
-        <v>510883000</v>
+        <v>470722000</v>
       </c>
       <c r="AS4" t="n">
         <v>412000</v>
       </c>
       <c r="AT4" t="n">
-        <v>510471000</v>
+        <v>470310000</v>
       </c>
       <c r="AU4" t="n">
-        <v>3178000</v>
+        <v>7643000</v>
       </c>
       <c r="AV4" t="n">
-        <v>15799000</v>
+        <v>-1844000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-6537000</v>
+        <v>14880000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>511884000</v>
-      </c>
+        <v>916323000</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>646461000</v>
+        <v>459664000</v>
       </c>
       <c r="C5" t="n">
-        <v>-2646647000</v>
+        <v>-2263734000</v>
       </c>
       <c r="D5" t="n">
-        <v>3267714000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6084000</v>
-      </c>
+        <v>1993593000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-686834000</v>
+        <v>-955826000</v>
       </c>
       <c r="G5" t="n">
-        <v>1643133000</v>
+        <v>2726060000</v>
       </c>
       <c r="H5" t="n">
-        <v>509639000</v>
+        <v>2840415000</v>
       </c>
       <c r="I5" t="n">
-        <v>-3761000</v>
+        <v>2681000</v>
       </c>
       <c r="J5" t="n">
-        <v>1137255000</v>
+        <v>-117036000</v>
       </c>
       <c r="K5" t="n">
-        <v>408778000</v>
+        <v>-647877000</v>
       </c>
       <c r="L5" t="n">
-        <v>-93139000</v>
+        <v>-128378000</v>
       </c>
       <c r="M5" t="n">
-        <v>-123631000</v>
+        <v>-245629000</v>
       </c>
       <c r="N5" t="n">
-        <v>-123631000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6084000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6084000</v>
-      </c>
+        <v>-245629000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>621067000</v>
+        <v>-270141000</v>
       </c>
       <c r="R5" t="n">
-        <v>621067000</v>
+        <v>-270141000</v>
       </c>
       <c r="S5" t="n">
-        <v>-2646647000</v>
+        <v>-2263734000</v>
       </c>
       <c r="T5" t="n">
-        <v>3267714000</v>
+        <v>1993593000</v>
       </c>
       <c r="U5" t="n">
-        <v>-604818000</v>
+        <v>-884649000</v>
       </c>
       <c r="V5" t="n">
-        <v>-38361000</v>
+        <v>-21881000</v>
       </c>
       <c r="W5" t="n">
-        <v>78083000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>27655000</v>
-      </c>
+        <v>46070000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>2678000</v>
+        <v>11186000</v>
       </c>
       <c r="Z5" t="n">
-        <v>28861000</v>
+        <v>11186000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-26183000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>9146000</v>
+        <v>15000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10000000</v>
+        <v>15000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-854000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-684019000</v>
+        <v>-951024000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2815000</v>
+        <v>4802000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-686834000</v>
+        <v>-955826000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1333295000</v>
+        <v>1415490000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-131549000</v>
+        <v>-206871000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-78506000</v>
+        <v>-29453000</v>
       </c>
       <c r="AK5" t="n">
-        <v>41779000</v>
+        <v>-33411000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1460768000</v>
+        <v>1522459000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-249000</v>
+        <v>-48600000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-356808000</v>
+        <v>-295133000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1223996000</v>
+        <v>-1174768000</v>
       </c>
       <c r="AP5" t="n">
-        <v>22980000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>627000</v>
-      </c>
+        <v>52879000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>384079000</v>
+        <v>579868000</v>
       </c>
       <c r="AS5" t="n">
-        <v>369000</v>
+        <v>1062000</v>
       </c>
       <c r="AT5" t="n">
-        <v>383710000</v>
+        <v>578806000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1319000</v>
+        <v>-2642000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2474000</v>
+        <v>-1938000</v>
       </c>
       <c r="AW5" t="n">
-        <v>3979000</v>
+        <v>370000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-7124000</v>
+        <v>-12960000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1055201000</v>
+        <v>965354000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>309222000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-2233426000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2331258000</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>-671178000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1647878000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2726060000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2357000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1075825000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-253236000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-107011000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-245511000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-245511000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>97832000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>97832000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-2233426000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2331258000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1802989000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-100330000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>88848000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>-1089102000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1089102000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-31779000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-31779000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-670626000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>552000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-671178000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>980400000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-155628000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-221883000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>151034000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-268688000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>35949000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-338368000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>198190000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5903000</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>658976000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>405000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>658571000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2468000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>456000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1068000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-1274000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>742272000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>10908000</v>
       </c>
     </row>
   </sheetData>
@@ -3299,7 +3517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ET2"/>
+  <dimension ref="A1:EU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3850,205 +4068,210 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>quoteSourceName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4070,10 +4293,8 @@
           <t>Foshan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>528137</t>
-        </is>
+      <c r="D2" t="n">
+        <v>528137</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4135,7 +4356,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Li  Wang', 'age': 46, 'title': 'Executive Chairman', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 2832815, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yuqing  Liao', 'age': 59, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 2203944, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Jianhua  Zheng', 'age': 51, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 2127506, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhihua  Wang', 'age': 54, 'title': 'Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 2156460, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yung Koon  Law', 'age': 68, 'title': 'Executive Director', 'yearBorn': 1957, 'fiscalYear': 2025, 'totalPay': 1005267, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianfeng  Luo', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 508424, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Ho  Pang CPA', 'age': 36, 'title': 'Company Secretary', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yuntang  Liu', 'age': 56, 'title': 'Deputy General Manager', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xikun  Wu', 'age': 53, 'title': 'Deputy GM of Guangdong Xingfa Group', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guan  Dubiao', 'age': 54, 'title': 'Deputy General Manager of Guangdong Xingfa', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Li  Wang', 'age': 46, 'title': 'Executive Chairman', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 2833101, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yuqing  Liao', 'age': 59, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 2204167, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Jianhua  Zheng', 'age': 51, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 2127721, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhihua  Wang', 'age': 54, 'title': 'Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 2156678, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yung Koon  Law', 'age': 68, 'title': 'Executive Director', 'yearBorn': 1957, 'fiscalYear': 2025, 'totalPay': 1005369, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianfeng  Luo', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 508476, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Ho  Pang CPA', 'age': 36, 'title': 'Company Secretary', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yuntang  Liu', 'age': 56, 'title': 'Deputy General Manager', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xikun  Wu', 'age': 53, 'title': 'Deputy GM of Guangdong Xingfa Group', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guan  Dubiao', 'age': 54, 'title': 'Deputy General Manager of Guangdong Xingfa', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4153,34 +4374,34 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="X2" t="n">
-        <v>7.11</v>
+        <v>6.76</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.11</v>
+        <v>6.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="AD2" t="n">
         <v>0.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>7.03</v>
+        <v>7.14</v>
       </c>
       <c r="AF2" t="n">
         <v>1780272000</v>
@@ -4192,34 +4413,34 @@
         <v>7.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.095</v>
+        <v>0.045</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.6395938</v>
+        <v>3.5532994</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.7471266</v>
+        <v>2.6819925</v>
       </c>
       <c r="AL2" t="n">
-        <v>9000</v>
+        <v>26000</v>
       </c>
       <c r="AM2" t="n">
-        <v>9000</v>
+        <v>26000</v>
       </c>
       <c r="AN2" t="n">
-        <v>40400</v>
+        <v>41866</v>
       </c>
       <c r="AO2" t="n">
-        <v>31200</v>
+        <v>54300</v>
       </c>
       <c r="AP2" t="n">
-        <v>31200</v>
+        <v>54300</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.17</v>
+        <v>6.99</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -4228,13 +4449,13 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3016054272</v>
+        <v>2944543744</v>
       </c>
       <c r="AV2" t="n">
-        <v>2990815342</v>
+        <v>2944543938</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.05</v>
+        <v>6.75</v>
       </c>
       <c r="AX2" t="n">
         <v>8.880000000000001</v>
@@ -4246,19 +4467,19 @@
         <v>0.53</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.14569934</v>
+        <v>0.14224482</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.5136</v>
+        <v>7.3868</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.59205</v>
+        <v>7.515</v>
       </c>
       <c r="BD2" t="n">
         <v>0.449</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.06315049</v>
+        <v>0.06414286</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -4269,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>3825848320</v>
+        <v>3754338048</v>
       </c>
       <c r="BI2" t="n">
         <v>0.030539999</v>
@@ -4290,10 +4511,10 @@
         <v>420649134</v>
       </c>
       <c r="BO2" t="n">
-        <v>17.302639</v>
+        <v>17.304386</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.41438767</v>
+        <v>0.4045217</v>
       </c>
       <c r="BQ2" t="n">
         <v>1767139200</v>
@@ -4320,16 +4541,16 @@
         <v>0.37</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.185</v>
+        <v>0.181</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.785</v>
+        <v>2.733</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.0481928</v>
+        <v>-0.12935323</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="CC2" t="n">
         <v>0.5</v>
@@ -4343,7 +4564,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -4432,153 +4653,158 @@
           <t>Equity</t>
         </is>
       </c>
-      <c r="DF2" t="b">
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DG2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DH2" t="n">
-        <v>-0.3435998</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.045730382</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.42205</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.055591047</v>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>XINGFA ALUM</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Xingfa Aluminium Holdings Limited</t>
+        </is>
       </c>
       <c r="DL2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="DN2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="b">
+      <c r="DO2" t="n">
+        <v>1206927000000</v>
+      </c>
+      <c r="DP2" t="n">
         <v>0</v>
       </c>
-      <c r="DP2" t="n">
-        <v>1206927000000</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.059999943</v>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>6.76 - 7.0</t>
+        </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>7.11 - 7.18</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
           <t>HKSE</t>
         </is>
       </c>
+      <c r="DS2" t="n">
+        <v>41866</v>
+      </c>
       <c r="DT2" t="n">
-        <v>40400</v>
+        <v>0.25</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.119999886</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.01702126</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>7.05 - 8.88</t>
-        </is>
+        <v>0.037037037</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>6.75 - 8.88</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-1.8800001</v>
       </c>
       <c r="DX2" t="n">
-        <v>-1.71</v>
+        <v>-0.21171172</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0.19256757</v>
+        <v>-12.935323</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-4.8192797</v>
+        <v>1756205940</v>
       </c>
       <c r="EA2" t="n">
-        <v>1756205940</v>
-      </c>
-      <c r="EB2" t="n">
         <v>1756728000</v>
       </c>
-      <c r="EC2" t="b">
+      <c r="EB2" t="b">
         <v>1</v>
       </c>
+      <c r="EC2" t="n">
+        <v>1.97</v>
+      </c>
       <c r="ED2" t="n">
-        <v>1.97</v>
+        <v>2.61</v>
       </c>
       <c r="EE2" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
+        <v>-0.3867998</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.052363653</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.51499987</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.06852959</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EH2" t="n">
-        <v>1780387096</v>
-      </c>
-      <c r="EI2" t="inlineStr">
+      <c r="EM2" t="n">
+        <v>1781596758</v>
+      </c>
+      <c r="EN2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>finmb_42410927</t>
         </is>
       </c>
-      <c r="EK2" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="EL2" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="EM2" t="n">
+      <c r="ER2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EN2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="EO2" t="b">
+      <c r="ET2" t="b">
         <v>0</v>
       </c>
-      <c r="EP2" t="n">
-        <v>0.8438811000000001</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>XINGFA ALUM</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>Xingfa Aluminium Holdings Limited</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
